--- a/test-data/CarLoanTestData.xlsx
+++ b/test-data/CarLoanTestData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2478620\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F96608D4-8CFD-4AF1-8C84-6F9C4D9AA24D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{35ED5EFB-BEF0-4E53-BF41-3380EE97985B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" xr2:uid="{1CC61DC1-D1E0-4F49-928F-2DBB17E33D24}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" xr2:uid="{C06392C3-B2F8-4A4B-BB2F-76D7B47CBD86}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,34 +38,34 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
-    <t>LoanAmount</t>
-  </si>
-  <si>
-    <t>InterestRate</t>
+    <t>Loan Amount</t>
+  </si>
+  <si>
+    <t>Interest Rate</t>
   </si>
   <si>
     <t>Tenure</t>
   </si>
   <si>
+    <t>Expected Amount</t>
+  </si>
+  <si>
+    <t>Actual Amount</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
     <t>TestCaseName</t>
   </si>
   <si>
-    <t>Expected EMI</t>
-  </si>
-  <si>
-    <t>Actual EMI</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
     <t>Car_15L_9.5_1yr</t>
   </si>
   <si>
-    <t>Car_20L_8.5_2yr</t>
-  </si>
-  <si>
-    <t>Car_50L_10_5yr</t>
+    <t>Car_20L_8.5_1yr</t>
+  </si>
+  <si>
+    <t>Car_50L_10_1yr</t>
   </si>
 </sst>
 </file>
@@ -436,15 +436,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F1A2503-9150-498C-8314-EC557360F5D4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD0AE97C-6A90-435A-BFB0-462DB7CBF186}">
   <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.453125" customWidth="1"/>
+    <col min="1" max="1" width="12.54296875" customWidth="1"/>
     <col min="2" max="2" width="11.54296875" customWidth="1"/>
-    <col min="4" max="4" width="15" customWidth="1"/>
-    <col min="5" max="5" width="12.81640625" customWidth="1"/>
-    <col min="6" max="6" width="11.1796875" customWidth="1"/>
+    <col min="4" max="4" width="16.54296875" customWidth="1"/>
+    <col min="5" max="5" width="15.6328125" customWidth="1"/>
+    <col min="6" max="6" width="12.54296875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
@@ -458,16 +458,16 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">

--- a/test-data/CarLoanTestData.xlsx
+++ b/test-data/CarLoanTestData.xlsx
@@ -3,12 +3,12 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2478620\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Final Project\emi-calculator-automation\test-data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{35ED5EFB-BEF0-4E53-BF41-3380EE97985B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C7D74B8-A45B-4E73-8F20-1AA01CF8A13E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" xr2:uid="{C06392C3-B2F8-4A4B-BB2F-76D7B47CBD86}"/>
   </bookViews>
@@ -17,7 +17,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="11">
   <si>
     <t>Loan Amount</t>
   </si>
@@ -66,13 +66,17 @@
   </si>
   <si>
     <t>Car_50L_10_1yr</t>
+  </si>
+  <si>
+    <t>PASS</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="0"/>
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -80,13 +84,67 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="17"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="17"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -101,8 +159,27 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -440,76 +517,103 @@
   <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.54296875" customWidth="1"/>
-    <col min="2" max="2" width="11.54296875" customWidth="1"/>
-    <col min="4" max="4" width="16.54296875" customWidth="1"/>
-    <col min="5" max="5" width="15.6328125" customWidth="1"/>
-    <col min="6" max="6" width="12.54296875" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="12.54296875"/>
+    <col min="2" max="2" customWidth="true" width="11.54296875"/>
+    <col min="4" max="4" customWidth="true" width="16.54296875"/>
+    <col min="5" max="5" customWidth="true" width="15.6328125"/>
+    <col min="6" max="6" customWidth="true" width="12.54296875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A2">
+      <c r="A2" s="0">
         <v>1500000</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="0">
         <v>9.5</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="0">
         <v>1</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" t="s" s="0">
         <v>7</v>
+      </c>
+      <c r="E2" t="n" s="0">
+        <v>131525.0</v>
+      </c>
+      <c r="F2" t="n" s="0">
+        <v>131525.0</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A3">
+      <c r="A3" s="0">
         <v>2000000</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="0">
         <v>8.5</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="0">
         <v>2</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" t="s" s="0">
         <v>8</v>
+      </c>
+      <c r="E3" s="0" t="n">
+        <v>90911.0</v>
+      </c>
+      <c r="F3" s="0" t="n">
+        <v>90911.0</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A4">
+      <c r="A4" s="0">
         <v>5000000</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="0">
         <v>10</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="0">
         <v>5</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" t="s" s="0">
         <v>9</v>
+      </c>
+      <c r="E4" s="0" t="n">
+        <v>106235.0</v>
+      </c>
+      <c r="F4" s="0" t="n">
+        <v>106235.0</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/test-data/CarLoanTestData.xlsx
+++ b/test-data/CarLoanTestData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Final Project\emi-calculator-automation\test-data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C7D74B8-A45B-4E73-8F20-1AA01CF8A13E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67A67B83-0AA7-44B9-9F13-3E1CF2E9658E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" xr2:uid="{C06392C3-B2F8-4A4B-BB2F-76D7B47CBD86}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="9">
   <si>
     <t>Loan Amount</t>
   </si>
@@ -60,12 +60,6 @@
   </si>
   <si>
     <t>Car_15L_9.5_1yr</t>
-  </si>
-  <si>
-    <t>Car_20L_8.5_1yr</t>
-  </si>
-  <si>
-    <t>Car_50L_10_1yr</t>
   </si>
   <si>
     <t>PASS</t>
@@ -76,7 +70,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -101,14 +95,9 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color indexed="9"/>
+      <color theme="1"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color indexed="9"/>
-      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -128,8 +117,20 @@
       <b val="true"/>
       <color indexed="9"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -142,12 +143,18 @@
       </patternFill>
     </fill>
     <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
       <patternFill patternType="none">
         <fgColor indexed="17"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -155,20 +162,45 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="2" tint="-0.249977111117893"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyAlignment="true" applyFill="true">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyAlignment="true" applyFill="true">
@@ -178,6 +210,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyAlignment="true" applyFill="true">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -514,7 +549,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD0AE97C-6A90-435A-BFB0-462DB7CBF186}">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="12.54296875"/>
@@ -566,55 +601,18 @@
       <c r="F2" t="n" s="0">
         <v>131525.0</v>
       </c>
-      <c r="G2" s="5" t="s">
-        <v>10</v>
+      <c r="G2" s="9" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A3" s="0">
-        <v>2000000</v>
-      </c>
-      <c r="B3" s="0">
-        <v>8.5</v>
-      </c>
-      <c r="C3" s="0">
-        <v>2</v>
-      </c>
-      <c r="D3" t="s" s="0">
-        <v>8</v>
-      </c>
-      <c r="E3" s="0" t="n">
-        <v>90911.0</v>
-      </c>
-      <c r="F3" s="0" t="n">
-        <v>90911.0</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>10</v>
-      </c>
+      <c r="G3" s="3"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A4" s="0">
-        <v>5000000</v>
-      </c>
-      <c r="B4" s="0">
-        <v>10</v>
-      </c>
-      <c r="C4" s="0">
-        <v>5</v>
-      </c>
-      <c r="D4" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="E4" s="0" t="n">
-        <v>106235.0</v>
-      </c>
-      <c r="F4" s="0" t="n">
-        <v>106235.0</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>10</v>
-      </c>
+      <c r="G4" s="3"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F15" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/test-data/CarLoanTestData.xlsx
+++ b/test-data/CarLoanTestData.xlsx
@@ -3,21 +3,22 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Final Project\emi-calculator-automation\test-data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67A67B83-0AA7-44B9-9F13-3E1CF2E9658E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D249C918-F2B3-40C7-BE75-23C88E4A33D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" xr2:uid="{C06392C3-B2F8-4A4B-BB2F-76D7B47CBD86}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" activeTab="1" xr2:uid="{C06392C3-B2F8-4A4B-BB2F-76D7B47CBD86}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="24">
   <si>
     <t>Loan Amount</t>
   </si>
@@ -63,14 +64,58 @@
   </si>
   <si>
     <t>PASS</t>
+  </si>
+  <si>
+    <t>Home Value</t>
+  </si>
+  <si>
+    <t>Loan Insurance</t>
+  </si>
+  <si>
+    <t>Loan Tenure</t>
+  </si>
+  <si>
+    <t>Loan Fees &amp; Charges</t>
+  </si>
+  <si>
+    <t>One Time Expenses</t>
+  </si>
+  <si>
+    <t>Maintanance Expenses</t>
+  </si>
+  <si>
+    <t>Home Insurance</t>
+  </si>
+  <si>
+    <t>Property Taxes</t>
+  </si>
+  <si>
+    <t>Expected Loan Amount</t>
+  </si>
+  <si>
+    <t>Actual Loan Amount</t>
+  </si>
+  <si>
+    <t>Expected EMI</t>
+  </si>
+  <si>
+    <t>Actual EMI</t>
+  </si>
+  <si>
+    <t>Expected Total Payment</t>
+  </si>
+  <si>
+    <t>Down  Payment</t>
+  </si>
+  <si>
+    <t>Actual Total Payment</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -89,48 +134,18 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color indexed="9"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
       <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -146,11 +161,6 @@
       <patternFill patternType="solid">
         <fgColor theme="0"/>
         <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="none">
-        <fgColor indexed="17"/>
       </patternFill>
     </fill>
   </fills>
@@ -190,29 +200,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyAlignment="true" applyFill="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyAlignment="true" applyFill="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyAlignment="true" applyFill="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyAlignment="true" applyFill="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyAlignment="true" applyFill="true">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -552,11 +547,11 @@
   <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="12.54296875"/>
-    <col min="2" max="2" customWidth="true" width="11.54296875"/>
-    <col min="4" max="4" customWidth="true" width="16.54296875"/>
-    <col min="5" max="5" customWidth="true" width="15.6328125"/>
-    <col min="6" max="6" customWidth="true" width="12.54296875"/>
+    <col min="1" max="1" width="12.54296875" customWidth="1"/>
+    <col min="2" max="2" width="11.54296875" customWidth="1"/>
+    <col min="4" max="4" width="16.54296875" customWidth="1"/>
+    <col min="5" max="5" width="15.6328125" customWidth="1"/>
+    <col min="6" max="6" width="12.54296875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
@@ -583,36 +578,114 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A2" s="0">
+      <c r="A2">
         <v>1500000</v>
       </c>
-      <c r="B2" s="0">
+      <c r="B2">
         <v>9.5</v>
       </c>
-      <c r="C2" s="0">
+      <c r="C2">
         <v>1</v>
       </c>
-      <c r="D2" t="s" s="0">
+      <c r="D2" t="s">
         <v>7</v>
       </c>
-      <c r="E2" t="n" s="0">
-        <v>131525.0</v>
-      </c>
-      <c r="F2" t="n" s="0">
-        <v>131525.0</v>
-      </c>
-      <c r="G2" s="9" t="s">
+      <c r="E2">
+        <v>131525</v>
+      </c>
+      <c r="F2">
+        <v>131525</v>
+      </c>
+      <c r="G2" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="G3" s="3"/>
+      <c r="G3" s="2"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="G4" s="3"/>
+      <c r="G4" s="2"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="F15" s="4"/>
+      <c r="F15" s="3"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D69B3FAA-C463-4541-8731-C2A4FE16588C}">
+  <dimension ref="A1:P1"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="10.7265625" customWidth="1"/>
+    <col min="2" max="2" width="13.1796875" customWidth="1"/>
+    <col min="3" max="3" width="13.08984375" customWidth="1"/>
+    <col min="4" max="4" width="11.36328125" customWidth="1"/>
+    <col min="5" max="5" width="11.7265625" customWidth="1"/>
+    <col min="6" max="6" width="18.453125" customWidth="1"/>
+    <col min="7" max="7" width="16.54296875" customWidth="1"/>
+    <col min="8" max="8" width="12.7265625" customWidth="1"/>
+    <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="10" max="10" width="19.81640625" customWidth="1"/>
+    <col min="11" max="11" width="19.08984375" customWidth="1"/>
+    <col min="12" max="12" width="16.81640625" customWidth="1"/>
+    <col min="13" max="13" width="12" customWidth="1"/>
+    <col min="14" max="14" width="9.1796875" customWidth="1"/>
+    <col min="15" max="15" width="19.90625" customWidth="1"/>
+    <col min="16" max="16" width="17.54296875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1" t="s">
+        <v>18</v>
+      </c>
+      <c r="M1" t="s">
+        <v>19</v>
+      </c>
+      <c r="N1" t="s">
+        <v>20</v>
+      </c>
+      <c r="O1" t="s">
+        <v>21</v>
+      </c>
+      <c r="P1" t="s">
+        <v>23</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/test-data/CarLoanTestData.xlsx
+++ b/test-data/CarLoanTestData.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="9">
   <si>
     <t>Loan Amount</t>
   </si>
@@ -70,7 +70,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -98,6 +98,12 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -190,7 +196,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -213,6 +219,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="true" applyAlignment="true" applyFill="true">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -601,7 +610,7 @@
       <c r="F2" t="n" s="0">
         <v>131525.0</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="G2" s="10" t="s">
         <v>8</v>
       </c>
     </row>
